--- a/public/uploads/files/sample_filter_upload.xlsx
+++ b/public/uploads/files/sample_filter_upload.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>filter_group_name</t>
   </si>
@@ -56,10 +56,16 @@
     <t>Inactive</t>
   </si>
   <si>
-    <t xml:space="preserve">Port </t>
+    <t>Port</t>
   </si>
   <si>
     <t>USB</t>
+  </si>
+  <si>
+    <t>No of Ports</t>
+  </si>
+  <si>
+    <t>"20"</t>
   </si>
 </sst>
 </file>
@@ -1212,8 +1218,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="3" outlineLevelCol="2"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18.8181818181818" customWidth="1"/>
     <col min="2" max="2" width="10.9090909090909" customWidth="1"/>
@@ -1264,6 +1270,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/uploads/files/sample_filter_upload.xlsx
+++ b/public/uploads/files/sample_filter_upload.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>filter_group_name</t>
   </si>
@@ -56,16 +56,13 @@
     <t>Inactive</t>
   </si>
   <si>
-    <t>Port</t>
+    <t xml:space="preserve">Port </t>
   </si>
   <si>
     <t>USB</t>
   </si>
   <si>
-    <t>No of Ports</t>
-  </si>
-  <si>
-    <t>"20"</t>
+    <t>no of ports</t>
   </si>
 </sst>
 </file>
@@ -681,9 +678,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1274,8 +1274,8 @@
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
+      <c r="B5" s="1">
+        <v>20</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>

--- a/public/uploads/files/sample_filter_upload.xlsx
+++ b/public/uploads/files/sample_filter_upload.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>filter_group_name</t>
   </si>
@@ -38,10 +38,10 @@
     <t>status</t>
   </si>
   <si>
-    <t>Category</t>
+    <t>Ac</t>
   </si>
   <si>
-    <t>Ac</t>
+    <t>1 ton</t>
   </si>
   <si>
     <t>Active</t>
@@ -56,13 +56,10 @@
     <t>Inactive</t>
   </si>
   <si>
-    <t xml:space="preserve">Port </t>
+    <t>Size</t>
   </si>
   <si>
-    <t>USB</t>
-  </si>
-  <si>
-    <t>no of ports</t>
+    <t>large</t>
   </si>
 </sst>
 </file>
@@ -1270,16 +1267,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1">
-        <v>20</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
+    <row r="5" spans="2:2">
+      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
